--- a/artfynd/A 10617-2025 artfynd.xlsx
+++ b/artfynd/A 10617-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22953</v>
+        <v>32222</v>
       </c>
       <c r="B2" t="n">
-        <v>57560</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100098</v>
+        <v>100021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lökgroda</t>
+          <t>Strandpadda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelobates fuscus</t>
+          <t>Epidalea calamita</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396299.0728421773</v>
+        <v>396299</v>
       </c>
       <c r="R2" t="n">
-        <v>6162016.132741854</v>
+        <v>6162016</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-03-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1992-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-07-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Saknas</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>32222</v>
+        <v>22953</v>
       </c>
       <c r="B3" t="n">
-        <v>57552</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100021</v>
+        <v>100098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strandpadda</t>
+          <t>Lökgroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epidalea calamita</t>
+          <t>Pelobates fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396299.0728421773</v>
+        <v>396299</v>
       </c>
       <c r="R3" t="n">
-        <v>6162016.132741854</v>
+        <v>6162016</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,27 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-03-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Saknas</t>
+          <t>1992-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
